--- a/artfynd/A 10626-2025 artfynd.xlsx
+++ b/artfynd/A 10626-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130153248</v>
       </c>
       <c r="B2" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 10626-2025 artfynd.xlsx
+++ b/artfynd/A 10626-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130153248</v>
       </c>
       <c r="B2" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 10626-2025 artfynd.xlsx
+++ b/artfynd/A 10626-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130153248</v>
       </c>
       <c r="B2" t="n">
-        <v>97791</v>
+        <v>97794</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 10626-2025 artfynd.xlsx
+++ b/artfynd/A 10626-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130153248</v>
       </c>
       <c r="B2" t="n">
-        <v>97794</v>
+        <v>97820</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 10626-2025 artfynd.xlsx
+++ b/artfynd/A 10626-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130153248</v>
       </c>
       <c r="B2" t="n">
-        <v>97820</v>
+        <v>97821</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 10626-2025 artfynd.xlsx
+++ b/artfynd/A 10626-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130153248</v>
       </c>
       <c r="B2" t="n">
-        <v>97821</v>
+        <v>97822</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
